--- a/data/trans_orig/P57GLOBAL_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>511638</t>
+          <t>511259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>554857</t>
+          <t>556628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>510587</t>
+          <t>512118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>553357</t>
+          <t>553664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1036701</t>
+          <t>1035744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1099177</t>
+          <t>1096149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139155</t>
+          <t>137384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182374</t>
+          <t>182753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133999</t>
+          <t>133692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176769</t>
+          <t>175238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282191</t>
+          <t>285219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344667</t>
+          <t>345624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>641787</t>
+          <t>644329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>702247</t>
+          <t>699051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>683858</t>
+          <t>686996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>741563</t>
+          <t>740596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1347183</t>
+          <t>1350813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1426459</t>
+          <t>1427974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258469</t>
+          <t>261665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318929</t>
+          <t>316387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225679</t>
+          <t>226646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>283384</t>
+          <t>280246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501499</t>
+          <t>499984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>580775</t>
+          <t>577145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>409783</t>
+          <t>413213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>462368</t>
+          <t>464263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440034</t>
+          <t>439438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>486217</t>
+          <t>485078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867204</t>
+          <t>863318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>937574</t>
+          <t>933798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214390</t>
+          <t>212495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266975</t>
+          <t>263545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197624</t>
+          <t>198763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>243807</t>
+          <t>244403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423025</t>
+          <t>426801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>493395</t>
+          <t>497281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>628518</t>
+          <t>626457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>683800</t>
+          <t>680524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>703997</t>
+          <t>702980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>761389</t>
+          <t>759742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1344423</t>
+          <t>1348290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1426942</t>
+          <t>1426122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255190</t>
+          <t>258466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310472</t>
+          <t>312533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276243</t>
+          <t>277890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333635</t>
+          <t>334652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>549680</t>
+          <t>550500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632199</t>
+          <t>628332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2250542</t>
+          <t>2250039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2354164</t>
+          <t>2355032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2385333</t>
+          <t>2385562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2485211</t>
+          <t>2491086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4661791</t>
+          <t>4665905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4811229</t>
+          <t>4815066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>916312</t>
+          <t>915444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1019934</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>890860</t>
+          <t>884985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>990738</t>
+          <t>990509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1835319</t>
+          <t>1831482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1984757</t>
+          <t>1980643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>421113</t>
+          <t>419590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>473203</t>
+          <t>470465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>474101</t>
+          <t>474434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>522351</t>
+          <t>523941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>909517</t>
+          <t>913134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>981174</t>
+          <t>980066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220754</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272844</t>
+          <t>274367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169000</t>
+          <t>167410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217250</t>
+          <t>216917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404133</t>
+          <t>405241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475790</t>
+          <t>472173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>660016</t>
+          <t>659294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>719651</t>
+          <t>723368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>729735</t>
+          <t>735568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>794500</t>
+          <t>796092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1413391</t>
+          <t>1415226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1497498</t>
+          <t>1499365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287601</t>
+          <t>283884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347236</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229397</t>
+          <t>227805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>288329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>533651</t>
+          <t>531784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>617758</t>
+          <t>615923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>464597</t>
+          <t>467736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>518328</t>
+          <t>522614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>516713</t>
+          <t>512937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>567250</t>
+          <t>567461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>996261</t>
+          <t>993743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1071765</t>
+          <t>1072219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228159</t>
+          <t>223873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281890</t>
+          <t>278751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205473</t>
+          <t>205262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256010</t>
+          <t>259786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447446</t>
+          <t>446992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522950</t>
+          <t>525468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>666606</t>
+          <t>672338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>724176</t>
+          <t>723997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>820194</t>
+          <t>820732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>870211</t>
+          <t>870628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1507358</t>
+          <t>1505774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1583041</t>
+          <t>1581857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214479</t>
+          <t>214658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272049</t>
+          <t>266317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164722</t>
+          <t>164305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214739</t>
+          <t>214201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390547</t>
+          <t>391731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>466230</t>
+          <t>467814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2280017</t>
+          <t>2278392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2384626</t>
+          <t>2391339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2596683</t>
+          <t>2599356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2703225</t>
+          <t>2702639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4901721</t>
+          <t>4910688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5060829</t>
+          <t>5064090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1001726</t>
+          <t>995013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1106335</t>
+          <t>1107960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>819678</t>
+          <t>820264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>926220</t>
+          <t>923547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1848426</t>
+          <t>1845165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2007534</t>
+          <t>1998567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016 (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>512478</t>
+          <t>511056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>555314</t>
+          <t>554554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>547750</t>
+          <t>547234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>585619</t>
+          <t>585564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1074094</t>
+          <t>1073460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1129723</t>
+          <t>1128350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116395</t>
+          <t>117155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159231</t>
+          <t>160653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82438</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120307</t>
+          <t>120823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210043</t>
+          <t>211416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265672</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>799052</t>
+          <t>803288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>850878</t>
+          <t>853426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>870135</t>
+          <t>874333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>916740</t>
+          <t>915370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1685257</t>
+          <t>1689269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1754548</t>
+          <t>1759292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165370</t>
+          <t>162822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217196</t>
+          <t>212960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118071</t>
+          <t>119441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164676</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296511</t>
+          <t>291767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>365802</t>
+          <t>361790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>625340</t>
+          <t>624640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>664227</t>
+          <t>665501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>640069</t>
+          <t>643684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>681149</t>
+          <t>682504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1279088</t>
+          <t>1281722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1337016</t>
+          <t>1336541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>84109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124270</t>
+          <t>124970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91109</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132189</t>
+          <t>128574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184853</t>
+          <t>185328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242781</t>
+          <t>240147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>724612</t>
+          <t>722230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>772464</t>
+          <t>771785</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>823572</t>
+          <t>824758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>873214</t>
+          <t>874637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1567231</t>
+          <t>1564094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1633854</t>
+          <t>1634776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157961</t>
+          <t>158640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205813</t>
+          <t>208195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>159001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210066</t>
+          <t>208880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330209</t>
+          <t>329287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396832</t>
+          <t>399969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2717762</t>
+          <t>2709949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2808146</t>
+          <t>2805215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +6014,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2975000</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2929722</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3018733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>84,79%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5733599</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>5672689</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5791798</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>83,38%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2788</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2975000</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2924839</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3015188</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5733599</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>5669921</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5799050</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>83,38%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559846</t>
+          <t>562777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>650230</t>
+          <t>658043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,82 +6127,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>533764</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>490031</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>579042</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1143157</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1084958</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1204067</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>16,62%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>533764</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>493576</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>583925</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1143157</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1077706</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1206835</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023 (tasa de respuesta: 98,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>337265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394150</t>
+          <t>394368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>389031</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>431016</t>
+          <t>430325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>741707</t>
+          <t>740102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>812629</t>
+          <t>807581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231992</t>
+          <t>231774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287190</t>
+          <t>288877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226348</t>
+          <t>227039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268333</t>
+          <t>270041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470877</t>
+          <t>475925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>543404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>334768</t>
+          <t>269845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>778747</t>
+          <t>776613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>612574</t>
+          <t>613722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>662683</t>
+          <t>664048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819664</t>
+          <t>812531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1424825</t>
+          <t>1423681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400628</t>
+          <t>402762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>844607</t>
+          <t>909530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>278057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329531</t>
+          <t>328383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696655</t>
+          <t>697799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1301816</t>
+          <t>1308949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>433295</t>
+          <t>428949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>492818</t>
+          <t>491728</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>382678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>482681</t>
+          <t>481850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>839081</t>
+          <t>835873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>956576</t>
+          <t>956366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204556</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264079</t>
+          <t>268425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237920</t>
+          <t>238751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344914</t>
+          <t>337923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>461398</t>
+          <t>461608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578893</t>
+          <t>582101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>527801</t>
+          <t>526530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>595335</t>
+          <t>590616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>484682</t>
+          <t>495158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>672553</t>
+          <t>674904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1025185</t>
+          <t>1053475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1238912</t>
+          <t>1244178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312793</t>
+          <t>317512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380327</t>
+          <t>381598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397335</t>
+          <t>394984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585206</t>
+          <t>574730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739104</t>
+          <t>733838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>952831</t>
+          <t>924541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1518941</t>
+          <t>1494593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2174881</t>
+          <t>2170174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1980925</t>
+          <t>1955444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2201273</t>
+          <t>2194019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3520377</t>
+          <t>3527222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4320061</t>
+          <t>4322024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1236137</t>
+          <t>1240844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1892077</t>
+          <t>1916425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1188685</t>
+          <t>1195939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1409033</t>
+          <t>1434514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2480916</t>
+          <t>2478953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3280600</t>
+          <t>3273755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57GLOBAL_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>511259</t>
+          <t>513082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>556628</t>
+          <t>555945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>512118</t>
+          <t>508065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>553664</t>
+          <t>552608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1035744</t>
+          <t>1033362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1096149</t>
+          <t>1097550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137384</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182753</t>
+          <t>180930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133692</t>
+          <t>134748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175238</t>
+          <t>179291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285219</t>
+          <t>283818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>345624</t>
+          <t>348006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>644329</t>
+          <t>646433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>699051</t>
+          <t>703415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686996</t>
+          <t>689290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>740596</t>
+          <t>741373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1350813</t>
+          <t>1347403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1427974</t>
+          <t>1428872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>261665</t>
+          <t>257301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316387</t>
+          <t>314283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226646</t>
+          <t>225869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280246</t>
+          <t>277952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499984</t>
+          <t>499086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>577145</t>
+          <t>580555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>413213</t>
+          <t>411182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>464263</t>
+          <t>464361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>439438</t>
+          <t>439782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>485078</t>
+          <t>485214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>863318</t>
+          <t>863857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>933798</t>
+          <t>935990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212495</t>
+          <t>212397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263545</t>
+          <t>265576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198763</t>
+          <t>198627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244403</t>
+          <t>244059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>426801</t>
+          <t>424609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>497281</t>
+          <t>496742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>626457</t>
+          <t>628083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>680524</t>
+          <t>683223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>702980</t>
+          <t>702115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>759742</t>
+          <t>760777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1348290</t>
+          <t>1348145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1426122</t>
+          <t>1427209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258466</t>
+          <t>255767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312533</t>
+          <t>310907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277890</t>
+          <t>276855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334652</t>
+          <t>335517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550500</t>
+          <t>549413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>628332</t>
+          <t>628477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2250039</t>
+          <t>2246459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2355032</t>
+          <t>2354550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2385562</t>
+          <t>2391150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2491086</t>
+          <t>2493440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4665905</t>
+          <t>4670773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4815066</t>
+          <t>4816316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>915444</t>
+          <t>915926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1024017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>882631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>990509</t>
+          <t>984921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1831482</t>
+          <t>1830232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1980643</t>
+          <t>1975775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419590</t>
+          <t>421203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>470465</t>
+          <t>472872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>474434</t>
+          <t>472438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>523941</t>
+          <t>521279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>913134</t>
+          <t>913222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>980066</t>
+          <t>982234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274367</t>
+          <t>272754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>170072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216917</t>
+          <t>218913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405241</t>
+          <t>403073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472173</t>
+          <t>472085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>659294</t>
+          <t>663195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>723368</t>
+          <t>724045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>735568</t>
+          <t>734821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>796092</t>
+          <t>795044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1415226</t>
+          <t>1416913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1499365</t>
+          <t>1498791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283884</t>
+          <t>283207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347958</t>
+          <t>344057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227805</t>
+          <t>228853</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288329</t>
+          <t>289076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>531784</t>
+          <t>532358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>615923</t>
+          <t>614236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>467736</t>
+          <t>466413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>522614</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>512937</t>
+          <t>513858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>567461</t>
+          <t>568381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>993743</t>
+          <t>997001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1072219</t>
+          <t>1073559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>223873</t>
+          <t>227293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278751</t>
+          <t>280074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205262</t>
+          <t>204342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259786</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>446992</t>
+          <t>445652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>525468</t>
+          <t>522210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>672338</t>
+          <t>671601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>726334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>820732</t>
+          <t>818944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>870628</t>
+          <t>869743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1505774</t>
+          <t>1508996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1581857</t>
+          <t>1577776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214658</t>
+          <t>212321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266317</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164305</t>
+          <t>165190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214201</t>
+          <t>215989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391731</t>
+          <t>395812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>467814</t>
+          <t>464592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2278392</t>
+          <t>2276496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2391339</t>
+          <t>2387681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2599356</t>
+          <t>2603273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2702639</t>
+          <t>2701715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4910688</t>
+          <t>4908312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5064090</t>
+          <t>5063081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>995013</t>
+          <t>998671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1107960</t>
+          <t>1109856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>820264</t>
+          <t>821188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>923547</t>
+          <t>919630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1845165</t>
+          <t>1846174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1998567</t>
+          <t>2000943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>511056</t>
+          <t>512229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>554554</t>
+          <t>554624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>547234</t>
+          <t>548632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>585564</t>
+          <t>583832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1073460</t>
+          <t>1072587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1128350</t>
+          <t>1128842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117155</t>
+          <t>117085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>159480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82493</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120823</t>
+          <t>119425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211416</t>
+          <t>210924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266306</t>
+          <t>267179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>803288</t>
+          <t>800775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>853426</t>
+          <t>852259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>874333</t>
+          <t>872656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>915370</t>
+          <t>914033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1689269</t>
+          <t>1686977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1759292</t>
+          <t>1757122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162822</t>
+          <t>163989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212960</t>
+          <t>215473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119441</t>
+          <t>120778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160478</t>
+          <t>162155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291767</t>
+          <t>293937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>361790</t>
+          <t>364082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624640</t>
+          <t>626847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>665501</t>
+          <t>663815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643684</t>
+          <t>641505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>682504</t>
+          <t>681175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1281722</t>
+          <t>1283723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1336541</t>
+          <t>1337252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84109</t>
+          <t>85795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124970</t>
+          <t>122763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89754</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128574</t>
+          <t>130753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185328</t>
+          <t>184617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240147</t>
+          <t>238146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722230</t>
+          <t>725151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>771785</t>
+          <t>774445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>824758</t>
+          <t>824013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>874637</t>
+          <t>872790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1564094</t>
+          <t>1562557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1634776</t>
+          <t>1632908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158640</t>
+          <t>155980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208195</t>
+          <t>205274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159001</t>
+          <t>160848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208880</t>
+          <t>209625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329287</t>
+          <t>331155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399969</t>
+          <t>401506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2709949</t>
+          <t>2710225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2805215</t>
+          <t>2804228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2929722</t>
+          <t>2925991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3018733</t>
+          <t>3014856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5672689</t>
+          <t>5663488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5791798</t>
+          <t>5792360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>562777</t>
+          <t>563764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>658043</t>
+          <t>657767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>490031</t>
+          <t>493908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579042</t>
+          <t>582773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1084958</t>
+          <t>1084396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1204067</t>
+          <t>1213268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>366661</t>
+          <t>405079</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337265</t>
+          <t>372942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394368</t>
+          <t>431446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>410341</t>
+          <t>448388</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>424670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>430325</t>
+          <t>470471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>853467</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>740102</t>
+          <t>815118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>807581</t>
+          <t>891013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>259481</t>
+          <t>275765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231774</t>
+          <t>249398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288877</t>
+          <t>307902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>247023</t>
+          <t>265873</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227039</t>
+          <t>243790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270041</t>
+          <t>289591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>506503</t>
+          <t>541638</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>475925</t>
+          <t>504092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543404</t>
+          <t>579987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>626142</t>
+          <t>680844</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>626142</t>
+          <t>680844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>626142</t>
+          <t>680844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>657364</t>
+          <t>714261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>657364</t>
+          <t>714261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>657364</t>
+          <t>714261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1283506</t>
+          <t>1395105</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1283506</t>
+          <t>1395105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1283506</t>
+          <t>1395105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>606276</t>
+          <t>680774</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269845</t>
+          <t>646095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>776613</t>
+          <t>715267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>639036</t>
+          <t>725136</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>613722</t>
+          <t>694546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>664048</t>
+          <t>749760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1245312</t>
+          <t>1405910</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812531</t>
+          <t>1357808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1423681</t>
+          <t>1447267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>573099</t>
+          <t>352550</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402762</t>
+          <t>318057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909530</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>303069</t>
+          <t>327232</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278057</t>
+          <t>302608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328383</t>
+          <t>357822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>876168</t>
+          <t>679782</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697799</t>
+          <t>638425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1308949</t>
+          <t>727884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1179375</t>
+          <t>1033324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1179375</t>
+          <t>1033324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1179375</t>
+          <t>1033324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942105</t>
+          <t>1052368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942105</t>
+          <t>1052368</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942105</t>
+          <t>1052368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2121480</t>
+          <t>2085692</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2121480</t>
+          <t>2085692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2121480</t>
+          <t>2085692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>462449</t>
+          <t>536061</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428949</t>
+          <t>505426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>491728</t>
+          <t>567972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>450379</t>
+          <t>527798</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382678</t>
+          <t>503663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>481850</t>
+          <t>553731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>912828</t>
+          <t>1063860</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>835873</t>
+          <t>1024536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>956366</t>
+          <t>1104925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>234925</t>
+          <t>257131</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>225220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268425</t>
+          <t>287766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>270222</t>
+          <t>273765</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238751</t>
+          <t>247832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337923</t>
+          <t>297900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>505146</t>
+          <t>530896</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>461608</t>
+          <t>489831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582101</t>
+          <t>570220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>697374</t>
+          <t>793192</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>697374</t>
+          <t>793192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>697374</t>
+          <t>793192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>720601</t>
+          <t>801563</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>720601</t>
+          <t>801563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>720601</t>
+          <t>801563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1417974</t>
+          <t>1594756</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1417974</t>
+          <t>1594756</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1417974</t>
+          <t>1594756</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>561085</t>
+          <t>616291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>526530</t>
+          <t>584671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>590616</t>
+          <t>648776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>620308</t>
+          <t>691012</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>495158</t>
+          <t>661683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>674904</t>
+          <t>719791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1181393</t>
+          <t>1307304</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1053475</t>
+          <t>1267513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1244178</t>
+          <t>1351774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>347043</t>
+          <t>355629</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317512</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>381598</t>
+          <t>387249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>449580</t>
+          <t>403406</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>394984</t>
+          <t>374627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>574730</t>
+          <t>432735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>796623</t>
+          <t>759035</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733838</t>
+          <t>714565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>924541</t>
+          <t>798826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>908128</t>
+          <t>971920</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>908128</t>
+          <t>971920</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>908128</t>
+          <t>971920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1069888</t>
+          <t>1094418</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1069888</t>
+          <t>1094418</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1069888</t>
+          <t>1094418</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1978016</t>
+          <t>2066339</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1978016</t>
+          <t>2066339</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1978016</t>
+          <t>2066339</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1494593</t>
+          <t>2176876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2170174</t>
+          <t>2301574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1955444</t>
+          <t>2340477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2194019</t>
+          <t>2443956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3527222</t>
+          <t>4547219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4322024</t>
+          <t>4719049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1414547</t>
+          <t>1241076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1240844</t>
+          <t>1177707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1916425</t>
+          <t>1302405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1269893</t>
+          <t>1270276</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1195939</t>
+          <t>1218655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1434514</t>
+          <t>1322134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2684441</t>
+          <t>2511352</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2478953</t>
+          <t>2422842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3273755</t>
+          <t>2594672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
